--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/70.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/70.xlsx
@@ -426,13 +426,13 @@
         <v>-19.40053935787692</v>
       </c>
       <c r="E2">
-        <v>-9.357826433591944</v>
+        <v>-6.024439358915831</v>
       </c>
       <c r="F2">
-        <v>-2.521001313781147</v>
+        <v>-2.20521440595553</v>
       </c>
       <c r="G2">
-        <v>-10.38979409729825</v>
+        <v>-7.959638486013149</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.53476046085637</v>
       </c>
       <c r="E3">
-        <v>-8.867247787392998</v>
+        <v>-6.220735121726318</v>
       </c>
       <c r="F3">
-        <v>-2.712963862236293</v>
+        <v>-1.960994299894777</v>
       </c>
       <c r="G3">
-        <v>-10.49475494362085</v>
+        <v>-8.453502359016085</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.55468780581247</v>
       </c>
       <c r="E4">
-        <v>-10.09977161500865</v>
+        <v>-7.363386854185749</v>
       </c>
       <c r="F4">
-        <v>-2.463595452767141</v>
+        <v>-2.24403004571591</v>
       </c>
       <c r="G4">
-        <v>-9.682529148288356</v>
+        <v>-8.235718120715131</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.42470754535813</v>
       </c>
       <c r="E5">
-        <v>-11.4612890247328</v>
+        <v>-7.596625907950811</v>
       </c>
       <c r="F5">
-        <v>-2.365824904949521</v>
+        <v>-2.474619366163597</v>
       </c>
       <c r="G5">
-        <v>-8.952858427068673</v>
+        <v>-7.533809634387774</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.13496515236942</v>
       </c>
       <c r="E6">
-        <v>-12.5304753233658</v>
+        <v>-9.126462168066057</v>
       </c>
       <c r="F6">
-        <v>-2.3086808080348</v>
+        <v>-2.349302288733282</v>
       </c>
       <c r="G6">
-        <v>-9.157221713753422</v>
+        <v>-6.998153434497079</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.69731659240988</v>
       </c>
       <c r="E7">
-        <v>-12.0126488490627</v>
+        <v>-9.773200711945506</v>
       </c>
       <c r="F7">
-        <v>-2.565753034349987</v>
+        <v>-2.123653351475891</v>
       </c>
       <c r="G7">
-        <v>-8.701750237369414</v>
+        <v>-7.004754662302386</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.13291872758986</v>
       </c>
       <c r="E8">
-        <v>-12.95184530130551</v>
+        <v>-9.661157208047726</v>
       </c>
       <c r="F8">
-        <v>-2.835906838690184</v>
+        <v>-1.886075923618187</v>
       </c>
       <c r="G8">
-        <v>-8.02572359606808</v>
+        <v>-7.455624480386807</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.48218975421122</v>
       </c>
       <c r="E9">
-        <v>-12.69183390920711</v>
+        <v>-10.82669584814192</v>
       </c>
       <c r="F9">
-        <v>-2.355638470997295</v>
+        <v>-2.384917116849244</v>
       </c>
       <c r="G9">
-        <v>-8.273461650408361</v>
+        <v>-5.345939608939771</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.79212186906544</v>
       </c>
       <c r="E10">
-        <v>-14.25514012071304</v>
+        <v>-11.78309144466587</v>
       </c>
       <c r="F10">
-        <v>-2.269634053769039</v>
+        <v>-2.189261706512418</v>
       </c>
       <c r="G10">
-        <v>-7.584000815308665</v>
+        <v>-5.945502579920558</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.11725920757589</v>
       </c>
       <c r="E11">
-        <v>-14.48300840430501</v>
+        <v>-11.09921488544952</v>
       </c>
       <c r="F11">
-        <v>-2.255612278741852</v>
+        <v>-2.399549398652295</v>
       </c>
       <c r="G11">
-        <v>-7.6499766773608</v>
+        <v>-5.38854964057573</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.51163237192216</v>
       </c>
       <c r="E12">
-        <v>-14.43799084419476</v>
+        <v>-12.05001781657399</v>
       </c>
       <c r="F12">
-        <v>-2.01041884098281</v>
+        <v>-2.397572085661812</v>
       </c>
       <c r="G12">
-        <v>-6.712135542086205</v>
+        <v>-4.346545500453507</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.0208242363776</v>
       </c>
       <c r="E13">
-        <v>-15.74255816479844</v>
+        <v>-12.69341887510979</v>
       </c>
       <c r="F13">
-        <v>-1.821351436600448</v>
+        <v>-2.548911496683671</v>
       </c>
       <c r="G13">
-        <v>-6.74295341051128</v>
+        <v>-4.108742393276579</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.68476668504219</v>
       </c>
       <c r="E14">
-        <v>-16.55390673885671</v>
+        <v>-14.01195653802714</v>
       </c>
       <c r="F14">
-        <v>-1.887599291271935</v>
+        <v>-1.831895725270683</v>
       </c>
       <c r="G14">
-        <v>-6.328287718444328</v>
+        <v>-3.19058907232403</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.52310234759177</v>
       </c>
       <c r="E15">
-        <v>-17.35258464264151</v>
+        <v>-14.23908215188184</v>
       </c>
       <c r="F15">
-        <v>-1.60362169171382</v>
+        <v>-1.404122656628004</v>
       </c>
       <c r="G15">
-        <v>-5.741476968880814</v>
+        <v>-3.758536333404777</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.54791291847771</v>
       </c>
       <c r="E16">
-        <v>-18.43215020370009</v>
+        <v>-15.83629304828321</v>
       </c>
       <c r="F16">
-        <v>-1.468991279573831</v>
+        <v>-1.425358683366172</v>
       </c>
       <c r="G16">
-        <v>-5.31028834402736</v>
+        <v>-2.782484881515913</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.74570045109128</v>
       </c>
       <c r="E17">
-        <v>-18.43446878239202</v>
+        <v>-16.11740712925736</v>
       </c>
       <c r="F17">
-        <v>-0.8494668961637196</v>
+        <v>-1.094640453105095</v>
       </c>
       <c r="G17">
-        <v>-5.024293625435261</v>
+        <v>-3.347826743257254</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.09943911183488</v>
       </c>
       <c r="E18">
-        <v>-19.0259644718519</v>
+        <v>-16.70435623081354</v>
       </c>
       <c r="F18">
-        <v>-0.5637737477144065</v>
+        <v>-0.8248511304221294</v>
       </c>
       <c r="G18">
-        <v>-4.702266929193735</v>
+        <v>-3.216937704271089</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.56665793371062</v>
       </c>
       <c r="E19">
-        <v>-21.18097921109607</v>
+        <v>-16.70871262280892</v>
       </c>
       <c r="F19">
-        <v>-0.7551821183770798</v>
+        <v>-0.2684251488180623</v>
       </c>
       <c r="G19">
-        <v>-4.67608382452364</v>
+        <v>-3.2419588074569</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-16.11028548846646</v>
       </c>
       <c r="E20">
-        <v>-21.33357067125853</v>
+        <v>-18.08467133614353</v>
       </c>
       <c r="F20">
-        <v>-0.4563262118972826</v>
+        <v>0.105055891877734</v>
       </c>
       <c r="G20">
-        <v>-5.527072797575455</v>
+        <v>-3.543897113366129</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-16.67318703705256</v>
       </c>
       <c r="E21">
-        <v>-22.10294934821371</v>
+        <v>-19.13005597539221</v>
       </c>
       <c r="F21">
-        <v>-0.2209166215327051</v>
+        <v>0.2690129951790345</v>
       </c>
       <c r="G21">
-        <v>-6.242220155514357</v>
+        <v>-3.104796284673817</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.21183988221668</v>
       </c>
       <c r="E22">
-        <v>-22.4113565420321</v>
+        <v>-18.34179809029905</v>
       </c>
       <c r="F22">
-        <v>-0.0002859340014735816</v>
+        <v>0.8600581072808986</v>
       </c>
       <c r="G22">
-        <v>-4.852668323588365</v>
+        <v>-3.786311810479262</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.67063668968284</v>
       </c>
       <c r="E23">
-        <v>-22.59078373916401</v>
+        <v>-19.47977190910856</v>
       </c>
       <c r="F23">
-        <v>0.2795846199735618</v>
+        <v>1.049797317626931</v>
       </c>
       <c r="G23">
-        <v>-5.350809421428039</v>
+        <v>-3.763813342994375</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-18.01653844599367</v>
       </c>
       <c r="E24">
-        <v>-22.49853419515376</v>
+        <v>-19.88642887499736</v>
       </c>
       <c r="F24">
-        <v>0.4792882618078694</v>
+        <v>1.37961345578636</v>
       </c>
       <c r="G24">
-        <v>-5.877100087988137</v>
+        <v>-3.895364491088394</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-18.21413662085967</v>
       </c>
       <c r="E25">
-        <v>-23.62733332562372</v>
+        <v>-20.23493570615366</v>
       </c>
       <c r="F25">
-        <v>0.3497291149078183</v>
+        <v>1.245760880637599</v>
       </c>
       <c r="G25">
-        <v>-6.023323573912206</v>
+        <v>-4.669558739265736</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-18.25495746494985</v>
       </c>
       <c r="E26">
-        <v>-22.38165880948979</v>
+        <v>-20.38774906154249</v>
       </c>
       <c r="F26">
-        <v>0.4587646310361089</v>
+        <v>1.038765120556447</v>
       </c>
       <c r="G26">
-        <v>-6.057634067881213</v>
+        <v>-4.706752718399447</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.13254866968715</v>
       </c>
       <c r="E27">
-        <v>-23.28878008033628</v>
+        <v>-20.54196624387371</v>
       </c>
       <c r="F27">
-        <v>0.5053926037722902</v>
+        <v>1.387342123654479</v>
       </c>
       <c r="G27">
-        <v>-5.686687440205876</v>
+        <v>-5.165902210877586</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-17.86619899851939</v>
       </c>
       <c r="E28">
-        <v>-22.54376912201637</v>
+        <v>-20.93113877161889</v>
       </c>
       <c r="F28">
-        <v>0.3635305442058609</v>
+        <v>0.8829972573992224</v>
       </c>
       <c r="G28">
-        <v>-7.154987218874512</v>
+        <v>-4.612839162541403</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.47740619004032</v>
       </c>
       <c r="E29">
-        <v>-23.34037298470567</v>
+        <v>-20.89170934843411</v>
       </c>
       <c r="F29">
-        <v>0.09199667977259975</v>
+        <v>0.9839288552259254</v>
       </c>
       <c r="G29">
-        <v>-6.539699156582187</v>
+        <v>-4.95066709264187</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.00325376991331</v>
       </c>
       <c r="E30">
-        <v>-23.06230203826467</v>
+        <v>-19.59594085282733</v>
       </c>
       <c r="F30">
-        <v>0.6292650084521227</v>
+        <v>1.010517792120984</v>
       </c>
       <c r="G30">
-        <v>-5.926344452884796</v>
+        <v>-4.714042539676923</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.4798249938581</v>
       </c>
       <c r="E31">
-        <v>-23.00808714744484</v>
+        <v>-19.62034027078065</v>
       </c>
       <c r="F31">
-        <v>-0.1018785690156105</v>
+        <v>0.7797230365574025</v>
       </c>
       <c r="G31">
-        <v>-4.985808533541234</v>
+        <v>-4.874739730698685</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.94538326957077</v>
       </c>
       <c r="E32">
-        <v>-22.5707633555761</v>
+        <v>-20.59969070204948</v>
       </c>
       <c r="F32">
-        <v>0.5994967974651196</v>
+        <v>0.8679077167898267</v>
       </c>
       <c r="G32">
-        <v>-5.225021933117891</v>
+        <v>-3.671978809734992</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.43575576408444</v>
       </c>
       <c r="E33">
-        <v>-21.45036907286437</v>
+        <v>-19.29594303524119</v>
       </c>
       <c r="F33">
-        <v>0.1970088154254931</v>
+        <v>0.1683183104295322</v>
       </c>
       <c r="G33">
-        <v>-5.152140273070836</v>
+        <v>-3.424061985935591</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.97660829014857</v>
       </c>
       <c r="E34">
-        <v>-21.70510479274384</v>
+        <v>-18.60814481753419</v>
       </c>
       <c r="F34">
-        <v>0.05508379993645098</v>
+        <v>0.5467720406443339</v>
       </c>
       <c r="G34">
-        <v>-5.37719777992157</v>
+        <v>-2.841680746303621</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.59328197551978</v>
       </c>
       <c r="E35">
-        <v>-21.76388891383741</v>
+        <v>-17.66936045642607</v>
       </c>
       <c r="F35">
-        <v>-0.4945843603955778</v>
+        <v>0.4509688654083627</v>
       </c>
       <c r="G35">
-        <v>-5.207956070862949</v>
+        <v>-2.555444357887156</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.29142496844618</v>
       </c>
       <c r="E36">
-        <v>-20.85499248117991</v>
+        <v>-18.10735446244795</v>
       </c>
       <c r="F36">
-        <v>-0.2879025515600871</v>
+        <v>0.5645471483736058</v>
       </c>
       <c r="G36">
-        <v>-4.080662346012481</v>
+        <v>-2.97641332866088</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.07947738117857</v>
       </c>
       <c r="E37">
-        <v>-20.90154066550476</v>
+        <v>-18.21580235798364</v>
       </c>
       <c r="F37">
-        <v>0.01275753912300743</v>
+        <v>0.09753100239070324</v>
       </c>
       <c r="G37">
-        <v>-4.880321310477897</v>
+        <v>-2.122802403541962</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.94407787343448</v>
       </c>
       <c r="E38">
-        <v>-20.90745938103278</v>
+        <v>-16.53954241930438</v>
       </c>
       <c r="F38">
-        <v>-0.05651054309908723</v>
+        <v>0.1934675447785252</v>
       </c>
       <c r="G38">
-        <v>-4.287240387663003</v>
+        <v>-1.850715286760341</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.87952316350165</v>
       </c>
       <c r="E39">
-        <v>-20.52391121800513</v>
+        <v>-16.48294102268251</v>
       </c>
       <c r="F39">
-        <v>-0.2905574690860596</v>
+        <v>-0.04111947675507241</v>
       </c>
       <c r="G39">
-        <v>-4.328555995993107</v>
+        <v>-1.305852459724932</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.86065111693696</v>
       </c>
       <c r="E40">
-        <v>-19.7370299890103</v>
+        <v>-16.12835697940791</v>
       </c>
       <c r="F40">
-        <v>-0.4284781565499688</v>
+        <v>0.1506368082167767</v>
       </c>
       <c r="G40">
-        <v>-2.937934857857931</v>
+        <v>-1.413173725017026</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.87534948403657</v>
       </c>
       <c r="E41">
-        <v>-19.76550050509653</v>
+        <v>-16.00890489203358</v>
       </c>
       <c r="F41">
-        <v>-0.3160446773353947</v>
+        <v>0.2241287358257461</v>
       </c>
       <c r="G41">
-        <v>-3.427379152565941</v>
+        <v>-1.139120144185078</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.89701138618552</v>
       </c>
       <c r="E42">
-        <v>-18.6834261694377</v>
+        <v>-14.44166343661498</v>
       </c>
       <c r="F42">
-        <v>-0.4974190336479577</v>
+        <v>-0.1293091271919134</v>
       </c>
       <c r="G42">
-        <v>-3.052122194598473</v>
+        <v>-1.137269549228626</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.91562989511487</v>
       </c>
       <c r="E43">
-        <v>-17.98840956416248</v>
+        <v>-14.09948288364739</v>
       </c>
       <c r="F43">
-        <v>-0.5454461189274674</v>
+        <v>-0.1967978762327947</v>
       </c>
       <c r="G43">
-        <v>-3.629554168649232</v>
+        <v>-1.708173127475942</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.91130273534811</v>
       </c>
       <c r="E44">
-        <v>-17.9658713490263</v>
+        <v>-14.48191251359515</v>
       </c>
       <c r="F44">
-        <v>-0.6387981550185549</v>
+        <v>-0.136301376438944</v>
       </c>
       <c r="G44">
-        <v>-3.013471575427482</v>
+        <v>-0.4734919264225955</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.8827100878941</v>
       </c>
       <c r="E45">
-        <v>-18.70938791092368</v>
+        <v>-13.53302512697592</v>
       </c>
       <c r="F45">
-        <v>-0.618197486078334</v>
+        <v>-0.3318325316653505</v>
       </c>
       <c r="G45">
-        <v>-3.150600992755173</v>
+        <v>-1.239075445652293</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.82260379986208</v>
       </c>
       <c r="E46">
-        <v>-16.53532641000324</v>
+        <v>-12.80739150893484</v>
       </c>
       <c r="F46">
-        <v>-1.066552999578372</v>
+        <v>0.1431757030197616</v>
       </c>
       <c r="G46">
-        <v>-3.889001622561915</v>
+        <v>-0.2676223415174774</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.74108048485625</v>
       </c>
       <c r="E47">
-        <v>-15.97391790185032</v>
+        <v>-13.0364417242428</v>
       </c>
       <c r="F47">
-        <v>-0.4973569060927477</v>
+        <v>-0.4351970445540756</v>
       </c>
       <c r="G47">
-        <v>-3.850801237584264</v>
+        <v>-1.201864913790885</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.64141884785916</v>
       </c>
       <c r="E48">
-        <v>-15.67240757394562</v>
+        <v>-12.49939187777715</v>
       </c>
       <c r="F48">
-        <v>-0.2314087230565637</v>
+        <v>-0.4723319268541746</v>
       </c>
       <c r="G48">
-        <v>-3.625445781634996</v>
+        <v>-0.4680758739203478</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.5398063270715</v>
       </c>
       <c r="E49">
-        <v>-15.57501368346265</v>
+        <v>-12.1227586945592</v>
       </c>
       <c r="F49">
-        <v>-0.6184526232383962</v>
+        <v>-0.3760772913836777</v>
       </c>
       <c r="G49">
-        <v>-4.385163014169105</v>
+        <v>-1.607267699438956</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.44491828968426</v>
       </c>
       <c r="E50">
-        <v>-14.80061292883297</v>
+        <v>-11.78054644227356</v>
       </c>
       <c r="F50">
-        <v>-0.9954683076419381</v>
+        <v>-0.223850698873421</v>
       </c>
       <c r="G50">
-        <v>-2.922083965815901</v>
+        <v>-1.379919295075047</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.37338997099883</v>
       </c>
       <c r="E51">
-        <v>-14.21826928534259</v>
+        <v>-11.23895906485222</v>
       </c>
       <c r="F51">
-        <v>-0.5772189790292452</v>
+        <v>-0.5313415071600003</v>
       </c>
       <c r="G51">
-        <v>-3.535514812060694</v>
+        <v>-1.339583608224566</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.33472387718823</v>
       </c>
       <c r="E52">
-        <v>-14.05455589301729</v>
+        <v>-10.61553310516426</v>
       </c>
       <c r="F52">
-        <v>-0.8740694080268648</v>
+        <v>-0.8556332631101591</v>
       </c>
       <c r="G52">
-        <v>-3.897026384949108</v>
+        <v>-1.868592232672406</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.34050383411997</v>
       </c>
       <c r="E53">
-        <v>-14.04368302692488</v>
+        <v>-10.25840858797135</v>
       </c>
       <c r="F53">
-        <v>-0.9624346723530993</v>
+        <v>-0.8373652767762216</v>
       </c>
       <c r="G53">
-        <v>-3.311493505963753</v>
+        <v>-2.204705300183531</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.39589019125466</v>
       </c>
       <c r="E54">
-        <v>-13.48086616335557</v>
+        <v>-9.70980660431213</v>
       </c>
       <c r="F54">
-        <v>-0.8733992587980001</v>
+        <v>-0.5111127751836363</v>
       </c>
       <c r="G54">
-        <v>-4.324477403888725</v>
+        <v>-2.415222891025786</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.50373443659498</v>
       </c>
       <c r="E55">
-        <v>-13.57393083268721</v>
+        <v>-10.31313066788004</v>
       </c>
       <c r="F55">
-        <v>0.02915175839181245</v>
+        <v>-0.6176457933880696</v>
       </c>
       <c r="G55">
-        <v>-4.672366081883037</v>
+        <v>-2.790569233722814</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.66326142538169</v>
       </c>
       <c r="E56">
-        <v>-12.37541131639515</v>
+        <v>-9.671060980702501</v>
       </c>
       <c r="F56">
-        <v>-0.8549954202100035</v>
+        <v>-0.6832930816925276</v>
       </c>
       <c r="G56">
-        <v>-5.040164380750528</v>
+        <v>-3.019043223570075</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.86691085212851</v>
       </c>
       <c r="E57">
-        <v>-12.44581097331839</v>
+        <v>-9.822724103693389</v>
       </c>
       <c r="F57">
-        <v>-1.339077591425381</v>
+        <v>-1.047340674405243</v>
       </c>
       <c r="G57">
-        <v>-5.52146473343193</v>
+        <v>-2.901018964549518</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.10802157482558</v>
       </c>
       <c r="E58">
-        <v>-11.78780105763385</v>
+        <v>-9.128305256987179</v>
       </c>
       <c r="F58">
-        <v>-0.4939316068821717</v>
+        <v>-0.7680756570016541</v>
       </c>
       <c r="G58">
-        <v>-5.625760160101129</v>
+        <v>-2.847656281002006</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.37086691369524</v>
       </c>
       <c r="E59">
-        <v>-11.06265198631159</v>
+        <v>-8.783330635556858</v>
       </c>
       <c r="F59">
-        <v>-1.329109846467495</v>
+        <v>-0.7781502613545017</v>
       </c>
       <c r="G59">
-        <v>-5.557635753994007</v>
+        <v>-3.610025260513071</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.64777535809613</v>
       </c>
       <c r="E60">
-        <v>-10.63180844074782</v>
+        <v>-8.45430982805556</v>
       </c>
       <c r="F60">
-        <v>-1.14390594765179</v>
+        <v>-0.6938448256693877</v>
       </c>
       <c r="G60">
-        <v>-5.895672248463448</v>
+        <v>-4.145926440773673</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.92223172075893</v>
       </c>
       <c r="E61">
-        <v>-11.3306923628256</v>
+        <v>-8.127127581001378</v>
       </c>
       <c r="F61">
-        <v>-0.6352080106948218</v>
+        <v>-0.8969861922253132</v>
       </c>
       <c r="G61">
-        <v>-5.754368233210736</v>
+        <v>-4.078086741582928</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.19142113603323</v>
       </c>
       <c r="E62">
-        <v>-11.01197836216576</v>
+        <v>-8.69968519216118</v>
       </c>
       <c r="F62">
-        <v>-1.075649302028513</v>
+        <v>-0.9286521929321299</v>
       </c>
       <c r="G62">
-        <v>-7.10126037531768</v>
+        <v>-4.092838532505921</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-15.44236435672101</v>
       </c>
       <c r="E63">
-        <v>-11.04073870058847</v>
+        <v>-7.555348867370896</v>
       </c>
       <c r="F63">
-        <v>-1.349891927868929</v>
+        <v>-0.6725723507654964</v>
       </c>
       <c r="G63">
-        <v>-6.597713156612375</v>
+        <v>-4.617636143027807</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.67817458426822</v>
       </c>
       <c r="E64">
-        <v>-10.97214590479429</v>
+        <v>-7.986767529133635</v>
       </c>
       <c r="F64">
-        <v>-1.205447847107973</v>
+        <v>-1.043624618236284</v>
       </c>
       <c r="G64">
-        <v>-6.128344010054506</v>
+        <v>-4.958231689199105</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.88942533704032</v>
       </c>
       <c r="E65">
-        <v>-10.91649095924002</v>
+        <v>-7.762377113579561</v>
       </c>
       <c r="F65">
-        <v>-1.088834425978873</v>
+        <v>-0.842999003482661</v>
       </c>
       <c r="G65">
-        <v>-7.952120237093464</v>
+        <v>-5.230153278703762</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.08338537265993</v>
       </c>
       <c r="E66">
-        <v>-10.0151344358053</v>
+        <v>-7.647485199530957</v>
       </c>
       <c r="F66">
-        <v>-1.235103400128196</v>
+        <v>-0.6778879843892608</v>
       </c>
       <c r="G66">
-        <v>-6.877785309234717</v>
+        <v>-4.729264428066492</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.25347602360926</v>
       </c>
       <c r="E67">
-        <v>-9.954009093649761</v>
+        <v>-8.287245364964587</v>
       </c>
       <c r="F67">
-        <v>-1.026285231760885</v>
+        <v>-0.9938811556981741</v>
       </c>
       <c r="G67">
-        <v>-6.779481969991599</v>
+        <v>-5.317154415475809</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.40891219503543</v>
       </c>
       <c r="E68">
-        <v>-10.12121846790898</v>
+        <v>-7.821442000061605</v>
       </c>
       <c r="F68">
-        <v>-0.9450439270987265</v>
+        <v>-0.8930638725730575</v>
       </c>
       <c r="G68">
-        <v>-7.58942679944753</v>
+        <v>-5.286581527420639</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.54481649339638</v>
       </c>
       <c r="E69">
-        <v>-9.830793844375059</v>
+        <v>-7.015015877249676</v>
       </c>
       <c r="F69">
-        <v>-0.8143954770639941</v>
+        <v>-0.9635546250816843</v>
       </c>
       <c r="G69">
-        <v>-6.556907372295318</v>
+        <v>-4.743794412438353</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-16.6696456115337</v>
       </c>
       <c r="E70">
-        <v>-9.70210819849909</v>
+        <v>-7.472523077770605</v>
       </c>
       <c r="F70">
-        <v>-1.008303860548316</v>
+        <v>-1.055789193546395</v>
       </c>
       <c r="G70">
-        <v>-7.556235269870797</v>
+        <v>-5.196289708382556</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-16.7795841475913</v>
       </c>
       <c r="E71">
-        <v>-10.48264503540917</v>
+        <v>-7.161453141235713</v>
       </c>
       <c r="F71">
-        <v>-1.091462835747956</v>
+        <v>-1.152993966427903</v>
       </c>
       <c r="G71">
-        <v>-6.704425281525243</v>
+        <v>-5.455320033557292</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-16.87999851275734</v>
       </c>
       <c r="E72">
-        <v>-10.37487641097463</v>
+        <v>-7.481100007541132</v>
       </c>
       <c r="F72">
-        <v>-1.267249853928636</v>
+        <v>-0.8136424910948493</v>
       </c>
       <c r="G72">
-        <v>-7.169676109432258</v>
+        <v>-5.666903620063191</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-16.96795692513952</v>
       </c>
       <c r="E73">
-        <v>-10.66938118958946</v>
+        <v>-7.905938796570727</v>
       </c>
       <c r="F73">
-        <v>-1.588996865217395</v>
+        <v>-1.027629672055629</v>
       </c>
       <c r="G73">
-        <v>-7.761611583490564</v>
+        <v>-5.116588324524603</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-17.04534602582152</v>
       </c>
       <c r="E74">
-        <v>-11.14861147992519</v>
+        <v>-8.868728598393506</v>
       </c>
       <c r="F74">
-        <v>-1.208936102241162</v>
+        <v>-1.022227888221973</v>
       </c>
       <c r="G74">
-        <v>-6.554249004227284</v>
+        <v>-4.478950769296658</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.11199993979099</v>
       </c>
       <c r="E75">
-        <v>-10.82569052691222</v>
+        <v>-8.227881599198035</v>
       </c>
       <c r="F75">
-        <v>-1.172979986755247</v>
+        <v>-1.038421642579301</v>
       </c>
       <c r="G75">
-        <v>-6.935577502713774</v>
+        <v>-5.38396453500384</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.16677561532906</v>
       </c>
       <c r="E76">
-        <v>-11.87691236915679</v>
+        <v>-8.504815898663109</v>
       </c>
       <c r="F76">
-        <v>-0.656125944350315</v>
+        <v>-1.083816176252714</v>
       </c>
       <c r="G76">
-        <v>-6.551825684892537</v>
+        <v>-5.160052476909694</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.21210247686388</v>
       </c>
       <c r="E77">
-        <v>-11.16244143954461</v>
+        <v>-10.04713263314349</v>
       </c>
       <c r="F77">
-        <v>-0.8474589335793336</v>
+        <v>-1.077626615018996</v>
       </c>
       <c r="G77">
-        <v>-7.20827375987462</v>
+        <v>-5.921438224395596</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.24409631574996</v>
       </c>
       <c r="E78">
-        <v>-11.28389058395632</v>
+        <v>-9.717418969119024</v>
       </c>
       <c r="F78">
-        <v>-1.638601990399238</v>
+        <v>-1.311632951003231</v>
       </c>
       <c r="G78">
-        <v>-7.330896366649226</v>
+        <v>-5.233940542800688</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.26813163177943</v>
       </c>
       <c r="E79">
-        <v>-13.13534359657032</v>
+        <v>-10.19948861265756</v>
       </c>
       <c r="F79">
-        <v>-1.560976509450299</v>
+        <v>-1.045701335315103</v>
       </c>
       <c r="G79">
-        <v>-6.733693814637939</v>
+        <v>-5.274752948208823</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.27952510921358</v>
       </c>
       <c r="E80">
-        <v>-13.78182854590534</v>
+        <v>-10.6355761311222</v>
       </c>
       <c r="F80">
-        <v>-1.498668370146526</v>
+        <v>-1.128927408274369</v>
       </c>
       <c r="G80">
-        <v>-7.365614057719562</v>
+        <v>-5.746820189381198</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.28775252324563</v>
       </c>
       <c r="E81">
-        <v>-12.97694663273003</v>
+        <v>-10.07903573252753</v>
       </c>
       <c r="F81">
-        <v>-1.625268588683777</v>
+        <v>-1.249196414752024</v>
       </c>
       <c r="G81">
-        <v>-6.305186731671294</v>
+        <v>-4.365276567114703</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.2894949009316</v>
       </c>
       <c r="E82">
-        <v>-15.5263914580423</v>
+        <v>-11.41239961934599</v>
       </c>
       <c r="F82">
-        <v>-1.748515575974496</v>
+        <v>-1.089865743395358</v>
       </c>
       <c r="G82">
-        <v>-7.706683011902976</v>
+        <v>-5.5657532116563</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-17.29784776070086</v>
       </c>
       <c r="E83">
-        <v>-15.89640854073503</v>
+        <v>-13.01513072556271</v>
       </c>
       <c r="F83">
-        <v>-1.860580431694824</v>
+        <v>-0.9227732694744618</v>
       </c>
       <c r="G83">
-        <v>-6.741016741370807</v>
+        <v>-4.752133676651777</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-17.30979242924977</v>
       </c>
       <c r="E84">
-        <v>-15.89327483672173</v>
+        <v>-12.96251438606759</v>
       </c>
       <c r="F84">
-        <v>-1.6734770864245</v>
+        <v>-1.074518580523692</v>
       </c>
       <c r="G84">
-        <v>-5.782709813572437</v>
+        <v>-5.532786799176237</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-17.33771862437448</v>
       </c>
       <c r="E85">
-        <v>-16.44693965432153</v>
+        <v>-13.79801784048277</v>
       </c>
       <c r="F85">
-        <v>-1.417402214462283</v>
+        <v>-1.245718100027669</v>
       </c>
       <c r="G85">
-        <v>-7.49226559841546</v>
+        <v>-5.14444656523757</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.37639112669666</v>
       </c>
       <c r="E86">
-        <v>-16.35377535856172</v>
+        <v>-15.43747034242768</v>
       </c>
       <c r="F86">
-        <v>-1.9370627656279</v>
+        <v>-1.157152370789957</v>
       </c>
       <c r="G86">
-        <v>-6.394402623409113</v>
+        <v>-5.206221345000371</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.43511950924493</v>
       </c>
       <c r="E87">
-        <v>-18.7752907931573</v>
+        <v>-16.02070609529757</v>
       </c>
       <c r="F87">
-        <v>-1.392061627243243</v>
+        <v>-1.262464375442663</v>
       </c>
       <c r="G87">
-        <v>-5.80063641766759</v>
+        <v>-5.11419480009971</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.50573321781569</v>
       </c>
       <c r="E88">
-        <v>-20.73711630276026</v>
+        <v>-16.92409137508773</v>
       </c>
       <c r="F88">
-        <v>-1.636303270856469</v>
+        <v>-1.125314069663358</v>
       </c>
       <c r="G88">
-        <v>-7.439101547600304</v>
+        <v>-5.775694767574722</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.59171421900114</v>
       </c>
       <c r="E89">
-        <v>-21.21881461143016</v>
+        <v>-18.39918744139826</v>
       </c>
       <c r="F89">
-        <v>-1.829539020009718</v>
+        <v>-1.141843312818819</v>
       </c>
       <c r="G89">
-        <v>-6.27599765165154</v>
+        <v>-5.677484123606702</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.68173890077021</v>
       </c>
       <c r="E90">
-        <v>-23.55562493971226</v>
+        <v>-21.02665334538867</v>
       </c>
       <c r="F90">
-        <v>-1.743442653999752</v>
+        <v>-0.8664119797553863</v>
       </c>
       <c r="G90">
-        <v>-7.183557226878422</v>
+        <v>-5.03896927381085</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.77380888996221</v>
       </c>
       <c r="E91">
-        <v>-24.34563534424639</v>
+        <v>-21.68045630872009</v>
       </c>
       <c r="F91">
-        <v>-1.434655450727791</v>
+        <v>-1.006010111209965</v>
       </c>
       <c r="G91">
-        <v>-7.002344585149796</v>
+        <v>-5.904266424683397</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.85731872479761</v>
       </c>
       <c r="E92">
-        <v>-26.97577757637534</v>
+        <v>-24.42785431832965</v>
       </c>
       <c r="F92">
-        <v>-1.126645256079656</v>
+        <v>-0.9522233873787899</v>
       </c>
       <c r="G92">
-        <v>-7.250721574779156</v>
+        <v>-5.32455348475608</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.92887338210212</v>
       </c>
       <c r="E93">
-        <v>-28.49242692018025</v>
+        <v>-25.79413568270986</v>
       </c>
       <c r="F93">
-        <v>-1.568088043603333</v>
+        <v>-0.703313065083386</v>
       </c>
       <c r="G93">
-        <v>-6.805502857930271</v>
+        <v>-6.939742169002177</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.98293627566381</v>
       </c>
       <c r="E94">
-        <v>-31.0158873616365</v>
+        <v>-28.24347859008258</v>
       </c>
       <c r="F94">
-        <v>-1.381629168172386</v>
+        <v>-0.7383372672411519</v>
       </c>
       <c r="G94">
-        <v>-7.816338211800256</v>
+        <v>-6.029808932623639</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.01746476709756</v>
       </c>
       <c r="E95">
-        <v>-31.82353164395649</v>
+        <v>-29.37592767060273</v>
       </c>
       <c r="F95">
-        <v>-1.158601185377453</v>
+        <v>-0.5848971164857939</v>
       </c>
       <c r="G95">
-        <v>-7.307126649677258</v>
+        <v>-6.964783135461225</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.03375429987856</v>
       </c>
       <c r="E96">
-        <v>-34.75938436363226</v>
+        <v>-31.03084038280983</v>
       </c>
       <c r="F96">
-        <v>-1.373770446622028</v>
+        <v>-0.7513053589319781</v>
       </c>
       <c r="G96">
-        <v>-8.282956295014991</v>
+        <v>-6.698959570839905</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.03005198773821</v>
       </c>
       <c r="E97">
-        <v>-38.67229837096598</v>
+        <v>-34.49954278930914</v>
       </c>
       <c r="F97">
-        <v>-0.9826385533073793</v>
+        <v>-0.4235601392795482</v>
       </c>
       <c r="G97">
-        <v>-8.804999531648203</v>
+        <v>-6.534273172443321</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.01404683871085</v>
       </c>
       <c r="E98">
-        <v>-39.81602108752822</v>
+        <v>-37.76578844411053</v>
       </c>
       <c r="F98">
-        <v>-1.520041077506156</v>
+        <v>-0.4634046113542044</v>
       </c>
       <c r="G98">
-        <v>-7.186725418959504</v>
+        <v>-6.521173343744425</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.98407577460623</v>
       </c>
       <c r="E99">
-        <v>-41.94413216269283</v>
+        <v>-39.60850829460074</v>
       </c>
       <c r="F99">
-        <v>-1.138085009912318</v>
+        <v>-0.4279687105972471</v>
       </c>
       <c r="G99">
-        <v>-7.367567279587733</v>
+        <v>-7.207240869666368</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.95296475067924</v>
       </c>
       <c r="E100">
-        <v>-44.38365960265391</v>
+        <v>-41.73024780683655</v>
       </c>
       <c r="F100">
-        <v>-1.085491963508577</v>
+        <v>0.0250496830131493</v>
       </c>
       <c r="G100">
-        <v>-8.409578040801035</v>
+        <v>-6.816536906212662</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.91955258305607</v>
       </c>
       <c r="E101">
-        <v>-45.88212259484402</v>
+        <v>-43.77535195344056</v>
       </c>
       <c r="F101">
-        <v>-1.227078176729874</v>
+        <v>0.03603466314167354</v>
       </c>
       <c r="G101">
-        <v>-9.249536276115998</v>
+        <v>-6.828593913066687</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.90170699068724</v>
       </c>
       <c r="E102">
-        <v>-49.43040613931713</v>
+        <v>-45.73099609602304</v>
       </c>
       <c r="F102">
-        <v>-0.9488453051101735</v>
+        <v>0.1007342991373289</v>
       </c>
       <c r="G102">
-        <v>-8.344886670418136</v>
+        <v>-7.064960243479571</v>
       </c>
     </row>
   </sheetData>
